--- a/output/pdf_financials_xlsx/MMG.xlsx
+++ b/output/pdf_financials_xlsx/MMG.xlsx
@@ -5664,31 +5664,31 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.826149</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.39199</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.438958</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.91229</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.240035</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.444612</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.921365</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.086732</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.858256</v>
       </c>
     </row>
     <row r="93">
@@ -9672,7 +9672,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10980,7 +10984,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -13258,7 +13266,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -14186,7 +14198,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -14368,7 +14384,11 @@
           <t>Share-based payment reserve (Note 9(d))</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MMG.xlsx
+++ b/output/pdf_financials_xlsx/MMG.xlsx
@@ -914,22 +914,22 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.374254</v>
+        <v>1.459015</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.325987</v>
+        <v>0.683812</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.058006</v>
+        <v>0.283863</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.029979</v>
+        <v>0.223185</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.015972</v>
+        <v>0.048137</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.05366</v>
+        <v>0.137574</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.68766</v>
@@ -953,10 +953,10 @@
         <v>4.992258</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.13212</v>
+        <v>6.197612</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.145836</v>
+        <v>4.208937</v>
       </c>
     </row>
     <row r="11">
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.370859</v>
+        <v>-1.45562</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.301968</v>
+        <v>-0.659793</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.015972</v>
+        <v>-0.048137</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.05366</v>
+        <v>-0.137574</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-0.68766</v>
@@ -1014,10 +1014,10 @@
         <v>-4.992258</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.13212</v>
+        <v>-6.197612</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.145836</v>
+        <v>-4.208937</v>
       </c>
     </row>
     <row r="12">
@@ -1050,13 +1050,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000646</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008352999999999999</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.027261</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1065,16 +1065,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.01525</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.06390899999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.063806</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.002127</v>
       </c>
     </row>
     <row r="13">
@@ -1909,16 +1909,16 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>2.9639</v>
+        <v>3.207819</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>36.731886</v>
+        <v>38.439626</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>55.094125</v>
+        <v>52.278276</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>62.906125</v>
+        <v>64.656481</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>107.1911</v>
@@ -1969,13 +1969,13 @@
         <v>-0.118556</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.571232</v>
+        <v>-2.570586</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.40753</v>
+        <v>-4.399177</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.516245</v>
+        <v>-2.488984</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-3.215733</v>
@@ -1984,16 +1984,16 @@
         <v>-7.492019</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-7.194474</v>
+        <v>-7.209724</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.922231</v>
+        <v>-4.98614</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-6.005512</v>
+        <v>-6.069318</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.781424</v>
+        <v>-3.783551</v>
       </c>
     </row>
     <row r="28">
@@ -2083,13 +2083,13 @@
         <v>-0.11712</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.571232</v>
+        <v>-2.570586</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.40753</v>
+        <v>-4.399177</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.51294</v>
+        <v>-2.485679</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-3.213703</v>
@@ -2098,16 +2098,16 @@
         <v>-7.489325</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-7.194474</v>
+        <v>-7.209724</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.922231</v>
+        <v>-4.98614</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.005512</v>
+        <v>-6.069318</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.781424</v>
+        <v>-3.783551</v>
       </c>
     </row>
     <row r="30">
@@ -2353,28 +2353,28 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.008293</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.002105</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000252</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.002766</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.710009</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.533023</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.367132</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.813348</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>1.300044</v>
@@ -2383,16 +2383,16 @@
         <v>4.023315</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.571865</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5.666316</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.398069</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>4.865265</v>
       </c>
     </row>
     <row r="35">
@@ -2463,28 +2463,28 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.008293</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.002105</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000252</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.002766</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.710009</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.533023</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.367132</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.813348</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>1.300044</v>
@@ -2493,16 +2493,16 @@
         <v>4.023315</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.571865</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>5.666316</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.398069</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>4.865265</v>
       </c>
     </row>
     <row r="37">
@@ -3123,19 +3123,19 @@
         <v>1.06359</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.042384</v>
+        <v>0.034091</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.030603</v>
+        <v>0.028498</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.024891</v>
+        <v>0.024639</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.020203</v>
+        <v>0.017437</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.722009</v>
+        <v>0.012</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>1.005299</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.804159</v>
+        <v>0.232294</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>6.609854</v>
+        <v>0.943538</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.819775</v>
+        <v>1.421706</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>5.341492</v>
+        <v>0.476227</v>
       </c>
     </row>
     <row r="49">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9294,7 +9294,11 @@
           <t>Reclamation deposit 8</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -11354,7 +11358,11 @@
           <t>Reclamation deposit 9</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -11540,7 +11548,11 @@
           <t>Reclamation deposit 10</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -14486,7 +14498,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -20736,7 +20748,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -21864,7 +21880,11 @@
           <t>Reclamation deposit 9</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -35090,7 +35110,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -35159,13 +35179,13 @@
         </is>
       </c>
       <c r="R286" s="5" t="n">
-        <v>-4.992258</v>
+        <v>4.992258</v>
       </c>
       <c r="S286" s="5" t="n">
-        <v>-6.197612</v>
+        <v>6.197612</v>
       </c>
       <c r="T286" s="5" t="n">
-        <v>-4.208937</v>
+        <v>4.208937</v>
       </c>
     </row>
     <row r="287">
@@ -35284,7 +35304,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -44778,7 +44798,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -45162,7 +45182,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -46678,7 +46698,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -47992,7 +48012,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -48006,19 +48026,19 @@
         </is>
       </c>
       <c r="G422" s="5" t="n">
-        <v>-0.683812</v>
+        <v>0.683812</v>
       </c>
       <c r="H422" s="5" t="n">
-        <v>-0.283863</v>
+        <v>0.283863</v>
       </c>
       <c r="I422" s="5" t="n">
-        <v>-0.223185</v>
+        <v>0.223185</v>
       </c>
       <c r="J422" s="5" t="n">
-        <v>-0.048137</v>
+        <v>0.048137</v>
       </c>
       <c r="K422" s="5" t="n">
-        <v>-0.137574</v>
+        <v>0.137574</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
@@ -52958,7 +52978,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -52967,10 +52987,10 @@
         </is>
       </c>
       <c r="F474" s="5" t="n">
-        <v>-1.459015</v>
+        <v>1.459015</v>
       </c>
       <c r="G474" s="5" t="n">
-        <v>-0.684351</v>
+        <v>0.684351</v>
       </c>
       <c r="H474" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MMG.xlsx
+++ b/output/pdf_financials_xlsx/MMG.xlsx
@@ -746,16 +746,16 @@
         <v>0.374254</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.325987</v>
+        <v>0.398311</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.058006</v>
+        <v>0.121767</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.029979</v>
+        <v>0.093447</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.015972</v>
+        <v>0.026699</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.05366</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.007305</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.284426</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.008293</v>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.007305</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.284426</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.008293</v>
@@ -3117,10 +3117,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.157556</v>
+        <v>0.150251</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.06359</v>
+        <v>0.779164</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.034091</v>
@@ -3398,22 +3398,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.003368</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.044196</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0</v>
+        <v>0.022711</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0</v>
+        <v>0.008835000000000001</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>0.003111</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0</v>
+        <v>0.001436</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
@@ -5419,22 +5419,22 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>1.757354</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>5.216368</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>5.371422</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>5.604185</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>5.739239</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>5.739239</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>5.977739</v>
@@ -5594,10 +5594,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.00735</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>0</v>
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.45018</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.267207</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -7083,10 +7083,10 @@
         <v>-0.071744</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>-0.005221</v>
+        <v>4.382048</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>-0.03385</v>
@@ -14862,7 +14862,11 @@
           <t>Equipment – Note 5</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -15608,7 +15612,11 @@
           <t>Share capital – Note 7</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -16256,7 +16264,11 @@
           <t>Equipment – Note 6</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -16440,7 +16452,11 @@
           <t>Exploration and evaluation assets – Notes 7 &amp; 10</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -16720,7 +16736,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -16896,7 +16916,11 @@
           <t>Accumulated comprehensive loss – Note 5</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -16990,7 +17014,11 @@
           <t>Prepaid expenses – Note 10</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -17182,7 +17210,11 @@
           <t>Cash – Note 5 $ 8,293 $</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="n">
         <v>0.007305</v>
       </c>
@@ -17560,7 +17592,11 @@
           <t>Prepaid expenses – Note 12 23,751</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
         <v>0.068037</v>
       </c>
@@ -17654,7 +17690,11 @@
           <t>Equipment – Note 7 22,711</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
         <v>0.003368</v>
       </c>
@@ -18622,7 +18662,11 @@
           <t>Share capital – Notes 8 and 10 5,371,422</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E112" s="5" t="n">
         <v>1.757354</v>
       </c>
@@ -18812,7 +18856,11 @@
           <t>Contributed surplus – Note 10 1,196,922</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>0.45018</v>
       </c>
@@ -27826,7 +27874,11 @@
           <t>Impairment of exploration and evaluation assets – Note 6</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -29232,7 +29284,11 @@
           <t>Impairment of exploration and evaluation assets - Note 6</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -47172,7 +47228,11 @@
           <t>Depreciation – Note 5</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -47730,7 +47790,11 @@
           <t>Office, rent and administration – Note 8</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -49632,7 +49696,11 @@
           <t>Office, rent and administration – Note 10</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MMG.xlsx
+++ b/output/pdf_financials_xlsx/MMG.xlsx
@@ -761,7 +761,7 @@
         <v>0.05366</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.68766</v>
+        <v>0.72766</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.437079</v>
@@ -932,7 +932,7 @@
         <v>0.137574</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.68766</v>
+        <v>0.72766</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>4.557875</v>
@@ -993,7 +993,7 @@
         <v>-0.137574</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.68766</v>
+        <v>-0.72766</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-4.557875</v>
@@ -6465,31 +6465,31 @@
         <v>0</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>0.691705</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>0.5239279999999999</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.208672</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.472238</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>1.306566</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.7495889999999999</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.681567</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.480247</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>0.46821</v>
       </c>
     </row>
     <row r="108">
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.057367</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002717</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -6696,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006749</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.017499</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.057367</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002717</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8043,10 +8043,10 @@
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006749</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.017499</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.856626</v>
+        <v>-0.9139930000000001</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.050894</v>
+        <v>-0.053611</v>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
@@ -8102,10 +8102,10 @@
         <v>-2.006334</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-3.116528</v>
+        <v>-3.123277</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-3.417199</v>
+        <v>-3.434698</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-2.104303</v>
@@ -19614,7 +19614,11 @@
           <t>Share-based payment expense 11e</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -21178,7 +21182,11 @@
           <t>Share-based payment expense 10e</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -24124,7 +24132,11 @@
           <t>Share-based payment expense 8(d)</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -24316,7 +24328,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -25470,7 +25486,11 @@
           <t>Share-based payment expense (Note 9)</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -26624,7 +26644,11 @@
           <t>Share-based payment expense (Note 9(d))</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -31864,7 +31888,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -32830,7 +32858,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -33406,7 +33438,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -45524,7 +45560,11 @@
           <t>Directors' fees (Note 14)</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -53240,7 +53280,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
